--- a/sprint 5/resultados.xlsx
+++ b/sprint 5/resultados.xlsx
@@ -30,12 +30,27 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -50,8 +65,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,11 +482,7 @@
           <t>Policy Brief / Informe técnico</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -486,11 +500,7 @@
           <t>Reporte institucional (Annual Report)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D3" s="1" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -508,11 +518,7 @@
           <t>Documento biográfico / perfiles académicos</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -530,11 +536,7 @@
           <t>Reporte institucional (Annual Report)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -552,11 +554,7 @@
           <t>Documento administrativo / electoral</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D6" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -616,11 +614,7 @@
           <t>Conference paper</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -638,11 +632,7 @@
           <t>Conference paper</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -660,11 +650,7 @@
           <t>Conference paper</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -682,11 +668,7 @@
           <t>Conference paper</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -704,11 +686,7 @@
           <t>Conference paper</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -726,11 +704,7 @@
           <t>Conference paper</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D7" s="1" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -748,11 +722,7 @@
           <t>Conference paper</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -770,11 +740,7 @@
           <t>Conference paper</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="D9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -792,11 +758,7 @@
           <t>Conference paper</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D10" s="1" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -814,11 +776,7 @@
           <t>Conference paper</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -836,11 +794,7 @@
           <t>Preprint (arXiv)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="D12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -858,11 +812,7 @@
           <t>Journal article / preprint</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -880,11 +830,7 @@
           <t>Conference paper</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -902,11 +848,7 @@
           <t>Conference paper (probable)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D15" s="1" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -924,11 +866,7 @@
           <t>Conference paper</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D16" s="1" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -946,11 +884,7 @@
           <t>Conference paper</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -968,11 +902,7 @@
           <t>Conference paper</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="D18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -990,11 +920,7 @@
           <t>Book chapter</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D19" s="1" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1012,11 +938,7 @@
           <t>Preprint (arXiv)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1034,11 +956,7 @@
           <t>Conference paper</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="D21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1056,11 +974,7 @@
           <t>Conference paper</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D22" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1131,11 +1045,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1158,11 +1068,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1185,11 +1091,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1212,11 +1114,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1239,11 +1137,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1266,11 +1160,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1293,11 +1183,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1320,11 +1206,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1347,11 +1229,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1374,11 +1252,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1401,11 +1275,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1428,11 +1298,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1455,11 +1321,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1482,11 +1344,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1509,11 +1367,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1536,11 +1390,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1563,11 +1413,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1590,11 +1436,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E19" s="1" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1617,11 +1459,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1644,11 +1482,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1671,11 +1505,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1698,11 +1528,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1725,11 +1551,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1752,11 +1574,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1779,11 +1597,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1806,11 +1620,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E27" s="1" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1833,11 +1643,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E28" s="1" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1860,11 +1666,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1887,11 +1689,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1914,11 +1712,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E31" s="1" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1941,11 +1735,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E32" s="1" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1968,11 +1758,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E33" s="1" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1995,11 +1781,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E34" s="1" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2022,11 +1804,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E35" s="1" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2049,11 +1827,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2076,11 +1850,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2103,11 +1873,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2130,11 +1896,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2157,11 +1919,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2184,11 +1942,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E41" s="1" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,11 +1965,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2238,11 +1988,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E43" s="1" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2265,11 +2011,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E44" s="1" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2292,11 +2034,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2319,11 +2057,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2346,11 +2080,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2373,11 +2103,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E48" s="1" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2400,11 +2126,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2427,11 +2149,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2454,11 +2172,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2481,11 +2195,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E52" s="1" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2508,11 +2218,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2535,11 +2241,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E54" s="1" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2562,11 +2264,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E55" s="1" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2589,11 +2287,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2616,11 +2310,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2643,11 +2333,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2670,11 +2356,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2697,11 +2379,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E60" s="1" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2724,11 +2402,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2751,11 +2425,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E62" s="1" t="n"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2778,11 +2448,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2805,11 +2471,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2832,11 +2494,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E65" s="1" t="n"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2859,11 +2517,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2886,11 +2540,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E67" s="1" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2913,11 +2563,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2940,11 +2586,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2967,11 +2609,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2994,11 +2632,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3021,11 +2655,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E72" s="1" t="n"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3048,11 +2678,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3075,11 +2701,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3102,11 +2724,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3129,11 +2747,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E76" s="1" t="n"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3156,11 +2770,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E77" s="1" t="n"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3183,11 +2793,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E78" s="1" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3210,11 +2816,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3237,11 +2839,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3264,11 +2862,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3291,11 +2885,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3318,11 +2908,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E83" s="1" t="n"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3345,11 +2931,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3372,11 +2954,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3399,11 +2977,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3426,11 +3000,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E87" s="1" t="n"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3453,11 +3023,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3480,11 +3046,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E89" s="1" t="n"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3507,11 +3069,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E90" s="3" t="n"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3534,11 +3092,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E91" s="1" t="n"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3561,11 +3115,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3588,11 +3138,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E93" s="1" t="n"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3615,11 +3161,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E94" s="1" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3642,11 +3184,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3669,11 +3207,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E96" s="1" t="n"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3696,11 +3230,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3723,11 +3253,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E98" s="1" t="n"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3750,11 +3276,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E99" s="1" t="n"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3777,11 +3299,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3804,11 +3322,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E101" s="1" t="n"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3831,11 +3345,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E102" s="1" t="n"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3858,11 +3368,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E103" s="1" t="n"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3885,11 +3391,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3912,11 +3414,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3939,11 +3437,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3966,11 +3460,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E107" s="1" t="n"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3993,11 +3483,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E108" s="1" t="n"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4020,11 +3506,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4047,11 +3529,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4074,11 +3552,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E111" s="1" t="n"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4101,11 +3575,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E112" s="3" t="n"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4128,11 +3598,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4155,11 +3621,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4182,11 +3644,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E115" s="1" t="n"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4209,11 +3667,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4236,11 +3690,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E117" s="3" t="n"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4263,11 +3713,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4290,11 +3736,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4317,11 +3759,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4344,11 +3782,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E121" s="1" t="n"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4371,11 +3805,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E122" s="1" t="n"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4398,11 +3828,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4425,11 +3851,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E124" s="1" t="n"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4452,11 +3874,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4479,11 +3897,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4506,11 +3920,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E127" s="1" t="n"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4533,11 +3943,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4560,11 +3966,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4587,11 +3989,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E130" s="1" t="n"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4614,11 +4012,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E131" s="3" t="n"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4641,11 +4035,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4668,11 +4058,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E133" s="1" t="n"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4695,11 +4081,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E134" s="1" t="n"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4722,11 +4104,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E135" s="1" t="n"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4749,11 +4127,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4776,11 +4150,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E137" s="1" t="n"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4803,11 +4173,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4830,11 +4196,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4857,11 +4219,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E140" s="3" t="n"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4884,11 +4242,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E141" s="1" t="n"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4911,11 +4265,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E142" s="1" t="n"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4938,11 +4288,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E143" s="1" t="n"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4965,11 +4311,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E144" s="1" t="n"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4992,11 +4334,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E145" s="1" t="n"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5019,11 +4357,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E146" s="1" t="n"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5046,11 +4380,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E147" s="1" t="n"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5073,11 +4403,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E148" s="1" t="n"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5100,11 +4426,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E149" s="1" t="n"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5127,11 +4449,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E150" s="1" t="n"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5154,11 +4472,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E151" s="1" t="n"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5181,11 +4495,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E152" s="3" t="n"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5208,11 +4518,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E153" s="1" t="n"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5235,11 +4541,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5262,11 +4564,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E155" s="1" t="n"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5289,11 +4587,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E156" s="1" t="n"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5316,11 +4610,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E157" s="1" t="n"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5343,11 +4633,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E158" s="1" t="n"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5370,11 +4656,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5397,11 +4679,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5424,11 +4702,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5451,11 +4725,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E162" s="1" t="n"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5478,11 +4748,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E163" s="1" t="n"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5505,11 +4771,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5532,11 +4794,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E165" s="1" t="n"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5559,11 +4817,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5586,11 +4840,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E167" s="1" t="n"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5613,11 +4863,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E168" s="1" t="n"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5640,11 +4886,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E169" s="1" t="n"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5667,11 +4909,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5694,11 +4932,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E171" s="1" t="n"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5721,11 +4955,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E172" s="3" t="n"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5748,11 +4978,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E173" s="1" t="n"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5775,11 +5001,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E174" s="1" t="n"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5802,11 +5024,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5829,11 +5047,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5856,11 +5070,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E177" s="1" t="n"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5883,11 +5093,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E178" s="1" t="n"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5910,11 +5116,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E179" s="3" t="n"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5937,11 +5139,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5964,11 +5162,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E181" s="1" t="n"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5991,11 +5185,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6018,11 +5208,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6045,11 +5231,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6072,11 +5254,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E185" s="1" t="n"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6099,11 +5277,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6126,11 +5300,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6153,11 +5323,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6180,11 +5346,7 @@
           <t>Research article</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6207,11 +5369,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6234,11 +5392,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E191" s="1" t="n"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6261,11 +5415,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E192" s="3" t="n"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6288,11 +5438,7 @@
           <t>Research article (Open access)</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E193" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6352,11 +5498,7 @@
           <t>Journal article</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6374,11 +5516,7 @@
           <t>Book chapter</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6396,11 +5534,7 @@
           <t>Book chapter</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6418,11 +5552,7 @@
           <t>Journal article</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6440,11 +5570,7 @@
           <t>Journal article</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6462,11 +5588,7 @@
           <t>Book chapter</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6484,11 +5606,7 @@
           <t>Book chapter</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6506,11 +5624,7 @@
           <t>Journal article</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6528,11 +5642,7 @@
           <t>Journal article</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6550,11 +5660,7 @@
           <t>Book chapter</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6572,11 +5678,7 @@
           <t>Book chapter</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6594,11 +5696,7 @@
           <t>Journal article</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6616,11 +5714,7 @@
           <t>Book chapter</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6638,11 +5732,7 @@
           <t>Journal article</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6660,11 +5750,7 @@
           <t>Journal article</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D16" s="1" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6682,11 +5768,7 @@
           <t>Journal article</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="D17" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6703,9 +5785,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -6744,7 +5826,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Balancing Innovation With Cybersecurity...</t>
+          <t>Balancing Innovation With Cybersecurity: Exploring the Role of Emerging Technologies in Digital Transformation for Socioeconomic Development in Nigeria</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6757,11 +5839,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6771,7 +5849,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Automation as an Equalizer...</t>
+          <t>Automation as an Equalizer: How Easy-to-Use Technologies Narrow Skill Gaps Between Low- and High-Skilled Workers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6784,11 +5862,7 @@
           <t>Survey Article</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6798,7 +5872,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Open strategy and digital transformation...</t>
+          <t>Open strategy and digital transformation: A framework and future research agenda</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6811,11 +5885,7 @@
           <t>Special Issue Article</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6825,7 +5895,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Materialising Design Fictions...</t>
+          <t>Materialising Design Fictions: Exploring Music Memorabilia in a Metaverse Environment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6838,11 +5908,7 @@
           <t>Special Issue Article</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6865,11 +5931,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6879,7 +5941,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ethical Principles of Integrating ChatGPT Into IoT...</t>
+          <t>Ethical Principles of Integrating ChatGPT Into IoT-Based Software Wearables</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6892,11 +5954,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6906,7 +5964,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bank Technology M&amp;As...</t>
+          <t>Bank Technology M&amp;As and Market Valuation: Lessons From the COVID-19 Shock</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6919,11 +5977,7 @@
           <t>Original Article</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E8" s="1" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6933,7 +5987,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Agentic AI Systems...</t>
+          <t>Agentic AI Systems: What It Is and Isn't</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6946,11 +6000,7 @@
           <t>Feature Article</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6960,7 +6010,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Investigating Developer Sentiments...</t>
+          <t>Investigating Developer Sentiments in Software Components</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6973,11 +6023,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6987,7 +6033,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A Review of TRiSM Frameworks...</t>
+          <t>A Review of TRiSM Frameworks in Artificial Intelligence Systems</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7000,11 +6046,7 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7014,7 +6056,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Regulation of Appropriate Prompts...</t>
+          <t>Regulation of Appropriate Prompts for Users in Text-Based Generative AI Programs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7027,11 +6069,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -7041,7 +6079,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Privacy preserving LLMs...</t>
+          <t>Privacy preserving large language models: ChatGPT case study</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -7054,11 +6092,7 @@
           <t>Case Study</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7068,7 +6102,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Conversational and generative AI...</t>
+          <t>Conversational and generative AI and human-chatbot interaction</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -7081,11 +6115,7 @@
           <t>Article</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7108,11 +6138,7 @@
           <t>Review Article</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7122,7 +6148,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AI in logistics and supply chain</t>
+          <t>Artificial intelligence in logistics and supply chain management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -7135,11 +6161,7 @@
           <t>Editorial</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E16" s="1" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -7162,11 +6184,7 @@
           <t>Article</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E17" s="1" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7176,7 +6194,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AI in innovation management</t>
+          <t>Artificial intelligence in innovation management</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -7189,11 +6207,7 @@
           <t>Original Article</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7203,7 +6217,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Building trust in AI</t>
+          <t>Building trust: Foundations of security, safety, and transparency in AI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -7216,11 +6230,7 @@
           <t>Article</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7230,7 +6240,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Attitudes toward AI</t>
+          <t>Attitudes toward artificial intelligence and globalization</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7243,11 +6253,7 @@
           <t>Article</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E20" s="1" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7270,11 +6276,7 @@
           <t>Symposium Paper</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7284,7 +6286,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Enterprise ICT software pricing...</t>
+          <t>Enterprise ICT software pricing and developer productivity measurement</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -7297,11 +6299,7 @@
           <t>Original Article</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7311,7 +6309,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AI literacy as a core component...</t>
+          <t>AI literacy as a core component of AI education</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7324,11 +6322,7 @@
           <t>Special Topic Article</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7338,7 +6332,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Emerging technologies and software processes</t>
+          <t>Special issues on emerging technologies and software processes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7351,11 +6345,7 @@
           <t>Editorial</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7365,7 +6355,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Innovation stakeholders...</t>
+          <t>Innovation stakeholders and sustainable paradigms</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7378,11 +6368,7 @@
           <t>Original Article</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E25" s="1" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7405,11 +6391,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7432,11 +6414,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7459,11 +6437,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7486,11 +6460,7 @@
           <t>Special Issue Article</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7513,11 +6483,7 @@
           <t>Article</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E30" s="1" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -7540,11 +6506,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -7567,11 +6529,7 @@
           <t>Special Issue Paper</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -7581,7 +6539,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>From Backlogs to Bots...</t>
+          <t>From Backlogs to Bots: Generative AI's Impact on Agile Roles</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -7594,11 +6552,7 @@
           <t>Methodology Paper</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -7608,7 +6562,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Generative AI in Early Childhood</t>
+          <t>Perspectives on Generative AI in Early Childhood</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -7621,11 +6575,7 @@
           <t>Perspective</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E34" s="1" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -7635,7 +6585,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Securing Software Development...</t>
+          <t>Securing Software Development Through People Maturity</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -7648,11 +6598,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -7662,7 +6608,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cybersecurity Framework for SDLC</t>
+          <t>Cybersecurity Framework for Software Development</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -7675,11 +6621,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -7702,11 +6644,7 @@
           <t>Special Issue Article</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7716,7 +6654,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Generative AI chatbots and DevOps</t>
+          <t>Generative AI chatbots and DevOps in Education 4.0</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7729,11 +6667,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7743,7 +6677,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Health info search + GenAI</t>
+          <t>Online Health Information Search in the Era of Generative AI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7756,11 +6690,7 @@
           <t>Long Paper</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E39" s="1" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7770,7 +6700,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Academic writing + GenAI</t>
+          <t>Future of Academic Writing in the Age of Generative AI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7783,11 +6713,7 @@
           <t>Panel</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E40" s="1" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7797,7 +6723,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GenAI + blockchain startups</t>
+          <t>Generative AI, Agentic AI, and Blockchain in Start-Ups</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7810,11 +6736,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7824,7 +6746,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GenAI methodological guidance</t>
+          <t>Generative AI Is Neither Just Another IT Artefact nor a Colleague: Methodological Guidance for IS Scholarship</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7837,11 +6759,7 @@
           <t>Editorial</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7851,7 +6769,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AI-Augmented Software Engineering</t>
+          <t>AI-Augmented Software Engineering: Revolutionizing or Challenging Software Quality and Testing?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -7861,14 +6779,10 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Special Issue</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+          <t>Special Issue - Technology Paper</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7878,24 +6792,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Healthcare + real-time software dev</t>
+          <t>Nurse and Other Healthcare Managers' Experiences and Recommendations for Patient Incident Reporting Processes and Real-Time Software Development: A Qualitative Study</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Nurse+...+Software+Development](https://onlinelibrary.wiley.com/action/doSearch?AllField=Nurse+...+Software+Development)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Nurse+and+Other+Healthcare+Managers+Experiences+and+Recommendations+for+Patient+Incident+Reporting+Processes+and+Real-Time+Software+Development](https://onlinelibrary.wiley.com/action/doSearch?AllField=Nurse+and+Other+Healthcare+Managers+Experiences+and+Recommendations+for+Patient+Incident+Reporting+Processes+and+Real-Time+Software+Development)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Empirical</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+          <t>Empirical Research Qualitative</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7905,12 +6815,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AI-enabled UX tools review</t>
+          <t>Designing With AI: A Systematic Literature Review on the Use, Development, and Perception of AI-Enabled UX Design Tools</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Designing+With+AI+A+Systematic](https://onlinelibrary.wiley.com/action/doSearch?AllField=Designing+With+AI+A+Systematic)...</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Designing+With+AI+A+Systematic+Literature+Review+on+the+Use+Development+and+Perception+of+AI-Enabled+UX+Design+Tools](https://onlinelibrary.wiley.com/action/doSearch?AllField=Designing+With+AI+A+Systematic+Literature+Review+on+the+Use+Development+and+Perception+of+AI-Enabled+UX+Design+Tools)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7918,11 +6828,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7932,12 +6838,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GenAI in agriculture</t>
+          <t>Determinants of Knowledge and Usage of Generative Artificial Intelligence in Agricultural Extension: Evidence From Tennessee Extension Personnel</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Determinants+of+Knowledge+](https://onlinelibrary.wiley.com/action/doSearch?AllField=Determinants+of+Knowledge+)...</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Determinants+of+Knowledge+and+Usage+of+Generative+Artificial+Intelligence+in+Agricultural+Extension](https://onlinelibrary.wiley.com/action/doSearch?AllField=Determinants+of+Knowledge+and+Usage+of+Generative+Artificial+Intelligence+in+Agricultural+Extension)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7945,11 +6851,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E46" s="1" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7959,7 +6861,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GenAI for Software Engineering</t>
+          <t>Generative Artificial Intelligence for Software Engineering-A Research Agenda</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7972,11 +6874,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7986,24 +6884,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Chatbot requirements sizing</t>
+          <t>Investigating the Effectiveness of COSMIC Method for Sizing Chatbots' Requirements: A Comparative Analysis</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=COSMIC+Method+Chatbots+Requirements](https://onlinelibrary.wiley.com/action/doSearch?AllField=COSMIC+Method+Chatbots+Requirements)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Investigating+the+Effectiveness+of+COSMIC+Method+for+Sizing+Chatbots+Requirements](https://onlinelibrary.wiley.com/action/doSearch?AllField=Investigating+the+Effectiveness+of+COSMIC+Method+for+Sizing+Chatbots+Requirements)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Empirical</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+          <t>Research Article - Empirical</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8013,12 +6907,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LLM for security documents</t>
+          <t>Integrating Large Language Model for Common Criteria Security Document Generation Based on PySide6</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Integrating+Large+Language+Model+](https://onlinelibrary.wiley.com/action/doSearch?AllField=Integrating+Large+Language+Model+)...</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Integrating+Large+Language+Model+for+Common+Criteria+Security+Document+Generation+Based+on+PySide6](https://onlinelibrary.wiley.com/action/doSearch?AllField=Integrating+Large+Language+Model+for+Common+Criteria+Security+Document+Generation+Based+on+PySide6)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8026,11 +6920,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8040,12 +6930,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Blockchain key management</t>
+          <t>Blockchain based secret key management for trusted platform module standard in reconfigurable platform</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Blockchain+secret+key+management](https://onlinelibrary.wiley.com/action/doSearch?AllField=Blockchain+secret+key+management)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Blockchain+based+secret+key+management+for+trusted+platform+module+standard+in+reconfigurable+platform](https://onlinelibrary.wiley.com/action/doSearch?AllField=Blockchain+based+secret+key+management+for+trusted+platform+module+standard+in+reconfigurable+platform)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8053,11 +6943,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E50" s="1" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8067,24 +6953,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AI in sports</t>
+          <t>Modern Advances in Artificial Intelligence Across the Athletic Domain</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+Athletic+Domain](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+Athletic+Domain)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Modern+Advances+in+Artificial+Intelligence+Across+the+Athletic+Domain](https://onlinelibrary.wiley.com/action/doSearch?AllField=Modern+Advances+in+Artificial+Intelligence+Across+the+Athletic+Domain)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Special Issue</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Special Issue Paper</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8094,24 +6976,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Confidential computing ML</t>
+          <t>Confidential Computing Across Edge-To-Cloud for Machine Learning: A Survey Study</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Confidential+Computing+ML](https://onlinelibrary.wiley.com/action/doSearch?AllField=Confidential+Computing+ML)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Confidential+Computing+Across+Edge-To-Cloud+for+Machine+Learning+A+Survey+Study](https://onlinelibrary.wiley.com/action/doSearch?AllField=Confidential+Computing+Across+Edge-To-Cloud+for+Machine+Learning+A+Survey+Study)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Survey</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Survey Article</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8121,12 +6999,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AI in marketing</t>
+          <t>Exploring the Impact of AI on Consumer Behavior and Digital Marketing Through the Lens of Social Media</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+consumer+behavior](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+consumer+behavior)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Exploring+the+Impact+of+AI+on+Consumer+Behavior+and+Digital+Marketing+Through+the+Lens+of+Social+Media](https://onlinelibrary.wiley.com/action/doSearch?AllField=Exploring+the+Impact+of+AI+on+Consumer+Behavior+and+Digital+Marketing+Through+the+Lens+of+Social+Media)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8134,11 +7012,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E53" s="1" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8148,12 +7022,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Microservices migration framework</t>
+          <t>Developing a Framework for the Quality-Driven Migration to Microservices: A Multi-Method Design Science Study</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Migration+to+Microservices](https://onlinelibrary.wiley.com/action/doSearch?AllField=Migration+to+Microservices)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Developing+a+Framework+for+the+Quality-Driven+Migration+to+Microservices](https://onlinelibrary.wiley.com/action/doSearch?AllField=Developing+a+Framework+for+the+Quality-Driven+Migration+to+Microservices)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8161,11 +7035,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8175,12 +7045,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AI impacts (social)</t>
+          <t>Exploring Some Impacts of Advances in Artificial Intelligence: A Social Informatics Approach</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Impacts+AI+Social](https://onlinelibrary.wiley.com/action/doSearch?AllField=Impacts+AI+Social)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Exploring+Some+Impacts+of+Advances+in+Artificial+Intelligence+A+Social+Informatics+Approach](https://onlinelibrary.wiley.com/action/doSearch?AllField=Exploring+Some+Impacts+of+Advances+in+Artificial+Intelligence+A+Social+Informatics+Approach)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8188,11 +7058,7 @@
           <t>Panel</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E55" s="1" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8202,12 +7068,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Smart mobility optimization</t>
+          <t>Multi-Modal Vaas Selection in Smart Mobility Networks via Spectral Hyper-Graph Clustering and Quantum-Driven Optimization</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Smart+Mobility+AI](https://onlinelibrary.wiley.com/action/doSearch?AllField=Smart+Mobility+AI)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Multi-Modal+Vaas+Selection+in+Smart+Mobility+Networks](https://onlinelibrary.wiley.com/action/doSearch?AllField=Multi-Modal+Vaas+Selection+in+Smart+Mobility+Networks)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8215,11 +7081,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E56" s="1" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8229,12 +7091,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Vehicle routing AI</t>
+          <t>AI-Infused Evolutionary Optimization for Multi-Depot Vehicle Routing: A Case Study of Beverage Distribution</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Vehicle+Routing+AI](https://onlinelibrary.wiley.com/action/doSearch?AllField=Vehicle+Routing+AI)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI-Infused+Evolutionary+Optimization+for+Multi-Depot+Vehicle+Routing](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI-Infused+Evolutionary+Optimization+for+Multi-Depot+Vehicle+Routing)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -8242,11 +7104,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E57" s="1" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8256,24 +7114,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Formal modeling survey</t>
+          <t>A comprehensive survey of UPPAAL-assisted formal modeling and verification</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=UPPAAL+formal+modeling](https://onlinelibrary.wiley.com/action/doSearch?AllField=UPPAAL+formal+modeling)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=A+comprehensive+survey+of+UPPAAL-assisted+formal+modeling+and+verification](https://onlinelibrary.wiley.com/action/doSearch?AllField=A+comprehensive+survey+of+UPPAAL-assisted+formal+modeling+and+verification)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Survey</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+          <t>Survey Article</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8283,12 +7137,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ethical AI governance lifecycle</t>
+          <t>Lifecycle-Based Governance to Build Reliable Ethical AI Systems</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Lifecycle+Governance+AI](https://onlinelibrary.wiley.com/action/doSearch?AllField=Lifecycle+Governance+AI)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Lifecycle-Based+Governance+to+Build+Reliable+Ethical+AI+Systems](https://onlinelibrary.wiley.com/action/doSearch?AllField=Lifecycle-Based+Governance+to+Build+Reliable+Ethical+AI+Systems)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -8296,11 +7150,7 @@
           <t>Research Article</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8310,24 +7160,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AI policy practice</t>
+          <t>AI Policy and Practice Across Your Institution: Lessons Learned</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+Policy+Practice](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+Policy+Practice)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+Policy+and+Practice+Across+Your+Institution+Lessons+Learned](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+Policy+and+Practice+Across+Your+Institution+Lessons+Learned)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Newsletter</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Newsletter Article</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8337,12 +7183,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Health info behaviors</t>
+          <t>Researching Health Information Behaviors: Landscape, AI's Role and Its Impact</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Health+Information+AI](https://onlinelibrary.wiley.com/action/doSearch?AllField=Health+Information+AI)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Researching+Health+Information+Behaviors+Landscape+AI+Role+and+Its+Impact](https://onlinelibrary.wiley.com/action/doSearch?AllField=Researching+Health+Information+Behaviors+Landscape+AI+Role+and+Its+Impact)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8350,11 +7196,7 @@
           <t>Panel</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E61" s="1" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8364,24 +7206,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AI platform orchestration</t>
+          <t>Orchestration logics for artificial intelligence platforms: From raw data to industry-specific applications</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+platform+orchestration](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+platform+orchestration)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Orchestration+logics+for+artificial+intelligence+platforms](https://onlinelibrary.wiley.com/action/doSearch?AllField=Orchestration+logics+for+artificial+intelligence+platforms)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Special Issue</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+          <t>Special Issue Article</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8391,24 +7229,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ChatGPT + decision making</t>
+          <t>Enhancing decision-making in higher education: Exploring the integration of ChatGPT and data visualization tools in data analysis</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=ChatGPT+decision+making](https://onlinelibrary.wiley.com/action/doSearch?AllField=ChatGPT+decision+making)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Enhancing+decision-making+in+higher+education+Exploring+the+integration+of+ChatGPT+and+data+visualization+tools+in+data+analysis](https://onlinelibrary.wiley.com/action/doSearch?AllField=Enhancing+decision-making+in+higher+education+Exploring+the+integration+of+ChatGPT+and+data+visualization+tools+in+data+analysis)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Practice</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+          <t>Practice and Policy</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8418,12 +7252,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Robotics supply chain</t>
+          <t>How Robotics is Shaping Digital Logistics and Supply Chain Management: An Ongoing Call for Research</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Robotics+supply+chain](https://onlinelibrary.wiley.com/action/doSearch?AllField=Robotics+supply+chain)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=How+Robotics+is+Shaping+Digital+Logistics+and+Supply+Chain+Management](https://onlinelibrary.wiley.com/action/doSearch?AllField=How+Robotics+is+Shaping+Digital+Logistics+and+Supply+Chain+Management)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8431,11 +7265,7 @@
           <t>Perspective</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E64" s="1" t="n"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8445,12 +7275,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Copyright economics</t>
+          <t>The economics of copyright in the digital age</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=copyright+economics](https://onlinelibrary.wiley.com/action/doSearch?AllField=copyright+economics)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=The+economics+of+copyright+in+the+digital+age](https://onlinelibrary.wiley.com/action/doSearch?AllField=The+economics+of+copyright+in+the+digital+age)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8458,11 +7288,7 @@
           <t>Article</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E65" s="1" t="n"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8472,12 +7298,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Gov info integration</t>
+          <t>Cross-Domain Information Integration in Government: Hierarchies and Responsibilities</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Government+information+integration](https://onlinelibrary.wiley.com/action/doSearch?AllField=Government+information+integration)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Cross-Domain+Information+Integration+in+Government+Hierarchies+and+Responsibilities](https://onlinelibrary.wiley.com/action/doSearch?AllField=Cross-Domain+Information+Integration+in+Government+Hierarchies+and+Responsibilities)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8485,11 +7311,7 @@
           <t>Long Paper</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E66" s="1" t="n"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8499,24 +7321,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Low-code/no-code development</t>
+          <t>Navigating Flexibility and Standardisation in Low-Code/No-Code Development</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Low-Code+No-Code+Development](https://onlinelibrary.wiley.com/action/doSearch?AllField=Low-Code+No-Code+Development)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Navigating+Flexibility+and+Standardisation+in+Low-Code+No-Code+Development](https://onlinelibrary.wiley.com/action/doSearch?AllField=Navigating+Flexibility+and+Standardisation+in+Low-Code+No-Code+Development)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Special Issue</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+          <t>Special Issue Article</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8526,24 +7344,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EU copyright originality</t>
+          <t>The elephant in the room of EU copyright originality: Time to unpack and harmonize the essential requirement of copyright</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=EU+copyright](https://onlinelibrary.wiley.com/action/doSearch?AllField=EU+copyright)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=The+elephant+in+the+room+of+EU+copyright+originality](https://onlinelibrary.wiley.com/action/doSearch?AllField=The+elephant+in+the+room+of+EU+copyright+originality)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Original</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Original Article</t>
+        </is>
+      </c>
+      <c r="E68" s="1" t="n"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8553,12 +7367,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AI-augmented professions</t>
+          <t>Information and library professionals' roles and responsibilities in an AI-augmented world</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+library+professionals](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+library+professionals)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Information+and+library+professionals+roles+and+responsibilities+in+an+AI-augmented+world](https://onlinelibrary.wiley.com/action/doSearch?AllField=Information+and+library+professionals+roles+and+responsibilities+in+an+AI-augmented+world)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8566,11 +7380,7 @@
           <t>Opinion</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E69" s="1" t="n"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8580,12 +7390,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Chatbot engineering survey</t>
+          <t>A Survey on Model-Driven Engineering and Domain-Specific Languages for Chatbot Development: Requirements, Challenges and Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Chatbot+development+requirements](https://onlinelibrary.wiley.com/action/doSearch?AllField=Chatbot+development+requirements)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=A+Survey+on+Model-Driven+Engineering+and+Domain-Specific+Languages+for+Chatbot+Development](https://onlinelibrary.wiley.com/action/doSearch?AllField=A+Survey+on+Model-Driven+Engineering+and+Domain-Specific+Languages+for+Chatbot+Development)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8593,11 +7403,7 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+      <c r="E70" s="3" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8607,24 +7413,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AI in speech therapy</t>
+          <t>The Application of Artificial Intelligence in Speech and Language Therapy: Attitudes and Expectations</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+speech+therapy](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+speech+therapy)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=The+Application+of+Artificial+Intelligence+in+Speech+and+Language+Therapy](https://onlinelibrary.wiley.com/action/doSearch?AllField=The+Application+of+Artificial+Intelligence+in+Speech+and+Language+Therapy)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Research Report</t>
+        </is>
+      </c>
+      <c r="E71" s="1" t="n"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8634,24 +7436,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AI education design</t>
+          <t>Systematically incorporating equity into design thinking for AI education</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+education+design](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+education+design)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Systematically+incorporating+equity+into+design+thinking+for+AI+education](https://onlinelibrary.wiley.com/action/doSearch?AllField=Systematically+incorporating+equity+into+design+thinking+for+AI+education)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Special Topic</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Special Topic Article</t>
+        </is>
+      </c>
+      <c r="E72" s="1" t="n"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8661,24 +7459,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Supply chain ecology</t>
+          <t>A systems perspective on the approach to industrial chain and supply chain ecology</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Supply+chain+ecology](https://onlinelibrary.wiley.com/action/doSearch?AllField=Supply+chain+ecology)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=A+systems+perspective+on+the+approach+to+industrial+chain+and+supply+chain+ecology](https://onlinelibrary.wiley.com/action/doSearch?AllField=A+systems+perspective+on+the+approach+to+industrial+chain+and+supply+chain+ecology)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Research Article</t>
+        </is>
+      </c>
+      <c r="E73" s="1" t="n"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8688,12 +7482,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AI materials manufacturing</t>
+          <t>Artificial intelligence enabled smart design and manufacturing of advanced materials: The endless Frontier in AI+ era</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+materials](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+materials)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Artificial+intelligence+enabled+smart+design+and+manufacturing+of+advanced+materials](https://onlinelibrary.wiley.com/action/doSearch?AllField=Artificial+intelligence+enabled+smart+design+and+manufacturing+of+advanced+materials)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -8701,11 +7495,7 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+      <c r="E74" s="1" t="n"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8715,24 +7505,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Metaverse review</t>
+          <t>Navigating the metaverse: A technical review of emerging virtual worlds</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Metaverse+review](https://onlinelibrary.wiley.com/action/doSearch?AllField=Metaverse+review)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Navigating+the+metaverse+A+technical+review+of+emerging+virtual+worlds](https://onlinelibrary.wiley.com/action/doSearch?AllField=Navigating+the+metaverse+A+technical+review+of+emerging+virtual+worlds)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Systematic Review</t>
+        </is>
+      </c>
+      <c r="E75" s="1" t="n"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8742,24 +7528,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AI insurance</t>
+          <t>Artificial Intelligence Applicability in the Insurance Industry: A Scientometric and Content Analysis Approach</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+insurance](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+insurance)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Artificial+Intelligence+Applicability+in+the+Insurance+Industry](https://onlinelibrary.wiley.com/action/doSearch?AllField=Artificial+Intelligence+Applicability+in+the+Insurance+Industry)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Research Article</t>
+        </is>
+      </c>
+      <c r="E76" s="1" t="n"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8769,24 +7551,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AI governance US</t>
+          <t>Towards Advancing AI Governance, Innovation, and Risk Management: US Government Agencies' Reflections</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+governance+US](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+governance+US)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Towards+Advancing+AI+Governance+Innovation+and+Risk+Management+US+Government+Agencies+Reflections](https://onlinelibrary.wiley.com/action/doSearch?AllField=Towards+Advancing+AI+Governance+Innovation+and+Risk+Management+US+Government+Agencies+Reflections)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+          <t>Long Paper</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8796,12 +7574,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NLP telecom specs</t>
+          <t>Technical Language Processing for Telecommunications Specifications</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=NLP+telecom](https://onlinelibrary.wiley.com/action/doSearch?AllField=NLP+telecom)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Technical+Language+Processing+for+Telecommunications+Specifications](https://onlinelibrary.wiley.com/action/doSearch?AllField=Technical+Language+Processing+for+Telecommunications+Specifications)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -8809,11 +7587,7 @@
           <t>Letter</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8823,24 +7597,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Agentic AI ecology</t>
+          <t>Automating Ecological and Fisheries Modelling With Agentic AI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Agentic+AI+ecology](https://onlinelibrary.wiley.com/action/doSearch?AllField=Agentic+AI+ecology)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Automating+Ecological+and+Fisheries+Modelling+With+Agentic+AI](https://onlinelibrary.wiley.com/action/doSearch?AllField=Automating+Ecological+and+Fisheries+Modelling+With+Agentic+AI)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Original</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Original Article</t>
+        </is>
+      </c>
+      <c r="E79" s="1" t="n"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8850,24 +7620,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Metaverse workplace</t>
+          <t>Openness to the Metaverse Workplace: Zoom Fatigue and Metaverse Information Seeking Mediate Gender Inequities</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Metaverse+workplace](https://onlinelibrary.wiley.com/action/doSearch?AllField=Metaverse+workplace)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Openness+to+the+Metaverse+Workplace+Zoom+Fatigue+and+Metaverse+Information+Seeking+Mediate+Gender+Inequities](https://onlinelibrary.wiley.com/action/doSearch?AllField=Openness+to+the+Metaverse+Workplace+Zoom+Fatigue+and+Metaverse+Information+Seeking+Mediate+Gender+Inequities)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Research Article</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8877,12 +7643,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AI@Work reflections</t>
+          <t>Studying AI in the Wild: Reflections from the AI@Work Research Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+at+Work](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+at+Work)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Studying+AI+in+the+Wild+Reflections+from+the+AI@Work+Research+Group](https://onlinelibrary.wiley.com/action/doSearch?AllField=Studying+AI+in+the+Wild+Reflections+from+the+AI@Work+Research+Group)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -8890,11 +7656,7 @@
           <t>Essay</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8904,24 +7666,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AI and innovation</t>
+          <t>Artificial intelligence use and scientific innovation</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+innovation](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+innovation)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Artificial+intelligence+use+and+scientific+innovation](https://onlinelibrary.wiley.com/action/doSearch?AllField=Artificial+intelligence+use+and+scientific+innovation)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+          <t>Research Article</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8931,24 +7689,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GPT-4 vs humans evaluation</t>
+          <t>A technological construction of society: Comparing GPT-4 and human respondents for occupational evaluation in the UK</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=GPT-4+evaluation](https://onlinelibrary.wiley.com/action/doSearch?AllField=GPT-4+evaluation)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=A+technological+construction+of+society+Comparing+GPT-4+and+human+respondents+for+occupational+evaluation+in+the+UK](https://onlinelibrary.wiley.com/action/doSearch?AllField=A+technological+construction+of+society+Comparing+GPT-4+and+human+respondents+for+occupational+evaluation+in+the+UK)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Original</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+          <t>Original Article</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8958,24 +7712,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IoV security survey</t>
+          <t>Securing the Road Ahead: A Survey on Internet of Vehicles Security Powered by a Conceptual Blockchain-Based Intrusion Detection System for Smart Cities</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=IoV+security](https://onlinelibrary.wiley.com/action/doSearch?AllField=IoV+security)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Securing+the+Road+Ahead+A+Survey+on+Internet+of+Vehicles+Security](https://onlinelibrary.wiley.com/action/doSearch?AllField=Securing+the+Road+Ahead+A+Survey+on+Internet+of+Vehicles+Security)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Survey</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Survey Article</t>
+        </is>
+      </c>
+      <c r="E84" s="1" t="n"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8985,24 +7735,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Strategic AI orientation</t>
+          <t>Strategic AI Orientation and Technological Innovation: Evidence From Managerial Insights and Panel Data</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Strategic+AI](https://onlinelibrary.wiley.com/action/doSearch?AllField=Strategic+AI)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Strategic+AI+Orientation+and+Technological+Innovation](https://onlinelibrary.wiley.com/action/doSearch?AllField=Strategic+AI+Orientation+and+Technological+Innovation)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Original</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+          <t>Original Article</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9012,12 +7758,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Rise of LLMs</t>
+          <t>The Rise of Large Language Models: Evolution, Applications, and Future Directions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=LLM+review](https://onlinelibrary.wiley.com/action/doSearch?AllField=LLM+review)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=The+Rise+of+Large+Language+Models+Evolution+Applications+and+Future+Directions](https://onlinelibrary.wiley.com/action/doSearch?AllField=The+Rise+of+Large+Language+Models+Evolution+Applications+and+Future+Directions)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -9025,11 +7771,7 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9039,24 +7781,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Online labour platforms</t>
+          <t>The duality of global online labour platforms as restrictive-expansive sites of workplace learning and skill development</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=online+labour](https://onlinelibrary.wiley.com/action/doSearch?AllField=online+labour)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=The+duality+of+global+online+labour+platforms+as+restrictive-expansive+sites+of+workplace+learning+and+skill+development](https://onlinelibrary.wiley.com/action/doSearch?AllField=The+duality+of+global+online+labour+platforms+as+restrictive-expansive+sites+of+workplace+learning+and+skill+development)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Research Article</t>
+        </is>
+      </c>
+      <c r="E87" s="1" t="n"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9066,24 +7804,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Analytics skills</t>
+          <t>The business analytics skills employers are looking for</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=analytics+skills](https://onlinelibrary.wiley.com/action/doSearch?AllField=analytics+skills)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=The+business+analytics+skills+employers+are+looking+for](https://onlinelibrary.wiley.com/action/doSearch?AllField=The+business+analytics+skills+employers+are+looking+for)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Empirical</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Empirical Research</t>
+        </is>
+      </c>
+      <c r="E88" s="1" t="n"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9093,24 +7827,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ML in requirements engineering</t>
+          <t>A systematic mapping to investigate the application of machine learning techniques in requirement engineering activities</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=ML+requirements+engineering](https://onlinelibrary.wiley.com/action/doSearch?AllField=ML+requirements+engineering)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=A+systematic+mapping+to+investigate+the+application+of+machine+learning+techniques+in+requirement+engineering+activities](https://onlinelibrary.wiley.com/action/doSearch?AllField=A+systematic+mapping+to+investigate+the+application+of+machine+learning+techniques+in+requirement+engineering+activities)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+          <t>Original Research</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9120,24 +7850,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Supply chain sustainability</t>
+          <t>How Revolutionising Supply Chains Contribute to Sustainable Development and Planning? A Systematic Literature Network Analysis of Platform-Based Ecosystems</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=supply+chain+sustainability](https://onlinelibrary.wiley.com/action/doSearch?AllField=supply+chain+sustainability)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=How+Revolutionising+Supply+Chains+Contribute+to+Sustainable+Development+and+Planning](https://onlinelibrary.wiley.com/action/doSearch?AllField=How+Revolutionising+Supply+Chains+Contribute+to+Sustainable+Development+and+Planning)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Review Article</t>
+        </is>
+      </c>
+      <c r="E90" s="1" t="n"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9147,24 +7873,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Fisheries research system</t>
+          <t>Implementing Reproducible Fisheries Research: A Decade of Experience With the Kahawai Reporting System</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=fisheries+system](https://onlinelibrary.wiley.com/action/doSearch?AllField=fisheries+system)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Implementing+Reproducible+Fisheries+Research+A+Decade+of+Experience+With+the+Kahawai+Reporting+System](https://onlinelibrary.wiley.com/action/doSearch?AllField=Implementing+Reproducible+Fisheries+Research+A+Decade+of+Experience+With+the+Kahawai+Reporting+System)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Research Article</t>
+        </is>
+      </c>
+      <c r="E91" s="1" t="n"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9174,24 +7896,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Info behavior trends</t>
+          <t>Trends in information behavior research, 2016-2022: An Annual Review of Information Science and Technology (ARIST) paper</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=information+behavior](https://onlinelibrary.wiley.com/action/doSearch?AllField=information+behavior)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Trends+in+information+behavior+research+2016+2022](https://onlinelibrary.wiley.com/action/doSearch?AllField=Trends+in+information+behavior+research+2016+2022)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Review Article</t>
+        </is>
+      </c>
+      <c r="E92" s="1" t="n"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9201,12 +7919,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AI decision-making</t>
+          <t>Intelligent Decision-Making Driven by Large AI Models: Progress, Challenges and Prospects</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+decision+making](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+decision+making)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Intelligent+Decision-Making+Driven+by+Large+AI+Models+Progress+Challenges+and+Prospects](https://onlinelibrary.wiley.com/action/doSearch?AllField=Intelligent+Decision-Making+Driven+by+Large+AI+Models+Progress+Challenges+and+Prospects)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -9214,11 +7932,7 @@
           <t>Review</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+      <c r="E93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9228,24 +7942,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>XR environments review</t>
+          <t>3D As-Built Environments in Extended Reality Applications: A Systematic Review</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=XR+review](https://onlinelibrary.wiley.com/action/doSearch?AllField=XR+review)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=3D+As-Built+Environments+in+Extended+Reality+Applications+A+Systematic+Review](https://onlinelibrary.wiley.com/action/doSearch?AllField=3D+As-Built+Environments+in+Extended+Reality+Applications+A+Systematic+Review)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Review Article</t>
+        </is>
+      </c>
+      <c r="E94" s="1" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9255,24 +7965,20 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ChatGPT across domains</t>
+          <t>ChatGPT Across Domains: A Systematic Review of Applications, Evaluation Approaches, and Open Challenges</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=ChatGPT+survey](https://onlinelibrary.wiley.com/action/doSearch?AllField=ChatGPT+survey)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=ChatGPT+Across+Domains+A+Systematic+Review+of+Applications+Evaluation+Approaches+and+Open+Challenges](https://onlinelibrary.wiley.com/action/doSearch?AllField=ChatGPT+Across+Domains+A+Systematic+Review+of+Applications+Evaluation+Approaches+and+Open+Challenges)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Survey</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+          <t>Survey Article</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9282,24 +7988,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>AI governance framework</t>
+          <t>A Framework for Evaluating Global AI Governance Initiatives</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+governance+framework](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+governance+framework)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=A+Framework+for+Evaluating+Global+AI+Governance+Initiatives](https://onlinelibrary.wiley.com/action/doSearch?AllField=A+Framework+for+Evaluating+Global+AI+Governance+Initiatives)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+          <t>Research Article</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9309,24 +8011,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>AI governance Nigeria</t>
+          <t>Where are the ethical guidelines? Examining the governance of digital technologies and AI in Nigeria</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+governance+Nigeria](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+governance+Nigeria)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Where+are+the+ethical+guidelines+Examining+the+governance+of+digital+technologies+and+AI+in+Nigeria](https://onlinelibrary.wiley.com/action/doSearch?AllField=Where+are+the+ethical+guidelines+Examining+the+governance+of+digital+technologies+and+AI+in+Nigeria)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Research Article</t>
+        </is>
+      </c>
+      <c r="E97" s="1" t="n"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9336,24 +8034,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>AI in healthcare</t>
+          <t>The promise of artificial intelligence in health: Portrayals of emerging healthcare technologies</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+healthcare](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+healthcare)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=The+promise+of+artificial+intelligence+in+health+Portrayals+of+emerging+healthcare+technologies](https://onlinelibrary.wiley.com/action/doSearch?AllField=The+promise+of+artificial+intelligence+in+health+Portrayals+of+emerging+healthcare+technologies)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Original</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Original Article</t>
+        </is>
+      </c>
+      <c r="E98" s="1" t="n"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9363,24 +8057,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Venture capital + AI</t>
+          <t>Gatekeepers of the Future: The Role of Corporate Venture Capital in Corporate Artificial Intelligence Adoptions</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+venture+capital](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+venture+capital)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Gatekeepers+of+the+Future+The+Role+of+Corporate+Venture+Capital+in+Corporate+Artificial+Intelligence+Adoptions](https://onlinelibrary.wiley.com/action/doSearch?AllField=Gatekeepers+of+the+Future+The+Role+of+Corporate+Venture+Capital+in+Corporate+Artificial+Intelligence+Adoptions)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>rojo</t>
-        </is>
-      </c>
+          <t>Research Article</t>
+        </is>
+      </c>
+      <c r="E99" s="1" t="n"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9390,24 +8080,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>AI audit function</t>
+          <t>Frontier AI developers need an internal audit function</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+audit](https://onlinelibrary.wiley.com/action/doSearch?AllField=AI+audit)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Frontier+AI+developers+need+an+internal+audit+function](https://onlinelibrary.wiley.com/action/doSearch?AllField=Frontier+AI+developers+need+an+internal+audit+function)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Original</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>amarillo</t>
-        </is>
-      </c>
+          <t>Original Article</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9417,24 +8103,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Multimodal LLM grading UML</t>
+          <t>Can Multimodal Large Language Models Grade Like an Expert? A Study on UML Class Diagram Assessment Accuracy</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=LLM+UML+grading](https://onlinelibrary.wiley.com/action/doSearch?AllField=LLM+UML+grading)</t>
+          <t>[https://onlinelibrary.wiley.com/action/doSearch?AllField=Can+Multimodal+Large+Language+Models+Grade+Like+an+Expert](https://onlinelibrary.wiley.com/action/doSearch?AllField=Can+Multimodal+Large+Language+Models+Grade+Like+an+Expert)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Research</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>verde</t>
-        </is>
-      </c>
+          <t>Research Article</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
